--- a/Кибер физ/3 лаба в методичке 7 лаба.xlsx
+++ b/Кибер физ/3 лаба в методичке 7 лаба.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filim\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\study\works\Кибер физ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C015EB33-6DD8-4DCE-8DA6-481DC19AEA98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A97693-F9EE-40A5-9F76-A8EA5B7E2658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="4" xr2:uid="{204A04D1-E1E4-4B3D-A404-03DEBDA79D09}"/>
   </bookViews>
@@ -19,9 +19,6 @@
     <sheet name="4" sheetId="4" r:id="rId4"/>
     <sheet name="5" sheetId="5" r:id="rId5"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId6"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
   <si>
     <t>Время формирования пакета, с</t>
   </si>
@@ -55,15 +52,6 @@
     <t>ts время занятия интерфейса маршрутизатора, с</t>
   </si>
   <si>
-    <t>Интерфейс</t>
-  </si>
-  <si>
-    <t>Время t, с</t>
-  </si>
-  <si>
-    <t>Функция распределения времени</t>
-  </si>
-  <si>
     <t>Общая длина пакета, Бит</t>
   </si>
   <si>
@@ -73,19 +61,39 @@
     <t>Скорость обслуживания, Бит/с</t>
   </si>
   <si>
-    <t>Скорость, Бит/с</t>
+    <t>Количество пользователей</t>
   </si>
   <si>
-    <t>Интенсивность</t>
+    <t>Интенсивность обслуживания, u</t>
+  </si>
+  <si>
+    <t>Длина пакета, бит</t>
+  </si>
+  <si>
+    <t>Скорость поступления, бит/c, VEL</t>
+  </si>
+  <si>
+    <t>lam</t>
+  </si>
+  <si>
+    <t>lam pac</t>
+  </si>
+  <si>
+    <t>нагррузка</t>
+  </si>
+  <si>
+    <t>время окончания обслуживания</t>
+  </si>
+  <si>
+    <t>ФРБ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="168" formatCode="0.0000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -219,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -255,29 +263,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -310,7 +300,37 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
@@ -331,85 +351,47 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'5'!$K$19:$L$29</c:f>
-              <c:strCache>
-                <c:ptCount val="11"/>
+          <c:val>
+            <c:numRef>
+              <c:f>'5'!$Q$3:$Q$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0,0001</c:v>
+                  <c:v>-1.0497756806822744E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0,0002</c:v>
+                  <c:v>-2.1105716511620631E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0,0003</c:v>
+                  <c:v>-3.1825035997616213E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0,0004</c:v>
+                  <c:v>-4.2656884292710195E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0,0005</c:v>
+                  <c:v>-5.3602442696974562E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0,0006</c:v>
+                  <c:v>-6.4662904911481744E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0,0007</c:v>
+                  <c:v>-7.5839477168488045E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0,0008</c:v>
+                  <c:v>-8.7133378362982183E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0,0009</c:v>
+                  <c:v>-0.1100781072570316</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0,001</c:v>
+                  <c:v>-0.2322734042113539</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'5'!$I$19:$I$29</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.17843225549402686</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.32502644118736801</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.4454634956851361</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.54441069490381055</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.62570252219107991</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.69248926538225097</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.74735909934872113</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.79243838508197117</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.82947407218577773</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.85990139810588095</c:v>
+                <c:pt idx="11">
+                  <c:v>-0.36791972817011875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -417,7 +399,38 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D106-4A23-B2A3-8B78AC28E5F9}"/>
+              <c16:uniqueId val="{00000000-7DB5-477F-A9B0-3100F01E5068}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'5'!$R$3:$R$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-7DB5-477F-A9B0-3100F01E5068}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -430,107 +443,16 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1292018431"/>
-        <c:axId val="1292014687"/>
-        <c:extLst>
-          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-            <c15:filteredLineSeries>
-              <c15:ser>
-                <c:idx val="1"/>
-                <c:order val="1"/>
-                <c:spPr>
-                  <a:ln w="28575" cap="rnd">
-                    <a:solidFill>
-                      <a:schemeClr val="accent2"/>
-                    </a:solidFill>
-                    <a:round/>
-                  </a:ln>
-                  <a:effectLst/>
-                </c:spPr>
-                <c:marker>
-                  <c:symbol val="none"/>
-                </c:marker>
-                <c:cat>
-                  <c:strRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'5'!$K$19:$L$29</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:strCache>
-                      <c:ptCount val="11"/>
-                      <c:pt idx="0">
-                        <c:v>0</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>0,0001</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>0,0002</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>0,0003</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>0,0004</c:v>
-                      </c:pt>
-                      <c:pt idx="5">
-                        <c:v>0,0005</c:v>
-                      </c:pt>
-                      <c:pt idx="6">
-                        <c:v>0,0006</c:v>
-                      </c:pt>
-                      <c:pt idx="7">
-                        <c:v>0,0007</c:v>
-                      </c:pt>
-                      <c:pt idx="8">
-                        <c:v>0,0008</c:v>
-                      </c:pt>
-                      <c:pt idx="9">
-                        <c:v>0,0009</c:v>
-                      </c:pt>
-                      <c:pt idx="10">
-                        <c:v>0,001</c:v>
-                      </c:pt>
-                    </c:strCache>
-                  </c:strRef>
-                </c:cat>
-                <c:val>
-                  <c:numRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'5'!$J$19:$J$29</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="11"/>
-                    </c:numCache>
-                  </c:numRef>
-                </c:val>
-                <c:smooth val="0"/>
-                <c:extLst>
-                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000001-D106-4A23-B2A3-8B78AC28E5F9}"/>
-                  </c:ext>
-                </c:extLst>
-              </c15:ser>
-            </c15:filteredLineSeries>
-          </c:ext>
-        </c:extLst>
+        <c:axId val="1166985743"/>
+        <c:axId val="899164623"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1292018431"/>
+        <c:axId val="1166985743"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -567,7 +489,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1292014687"/>
+        <c:crossAx val="899164623"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -575,7 +497,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1292014687"/>
+        <c:axId val="899164623"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -626,7 +548,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1292018431"/>
+        <c:crossAx val="1166985743"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -727,19 +649,69 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>маршрутизатор</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" baseline="0"/>
+              <a:t> 2</a:t>
+            </a:r>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="6.7261592300962375E-2"/>
-          <c:y val="7.8703703703703706E-2"/>
-          <c:w val="0.8966272965879265"/>
-          <c:h val="0.73577136191309422"/>
-        </c:manualLayout>
-      </c:layout>
+      <c:layout/>
       <c:lineChart>
         <c:grouping val="stacked"/>
         <c:varyColors val="0"/>
@@ -758,85 +730,47 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'5'!$K$4:$L$14</c:f>
-              <c:strCache>
-                <c:ptCount val="11"/>
+          <c:val>
+            <c:numRef>
+              <c:f>'5'!$Q$22:$Q$33</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.0001</c:v>
+                  <c:v>0.25824934618682516</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.0002</c:v>
+                  <c:v>0.44980596756772784</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.0003</c:v>
+                  <c:v>0.59189321671925499</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.0004</c:v>
+                  <c:v>0.69728652667591584</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.0005</c:v>
+                  <c:v>0.7754620832438035</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.0006</c:v>
+                  <c:v>0.833448853440243</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.0007</c:v>
+                  <c:v>0.87646057814596645</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.0008</c:v>
+                  <c:v>0.90836455306806896</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.0009</c:v>
+                  <c:v>0.9495827239387874</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.001</c:v>
+                  <c:v>0.99745809827456744</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'5'!$I$4:$I$14</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.32670359327284115</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.54667194868829627</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.6947758519832048</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.79449367789393333</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.86163333176627122</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.90683821946742149</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.93727450792311073</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.95776715157443759</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.97156477490921611</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.98085466512189723</c:v>
+                <c:pt idx="11">
+                  <c:v>0.99987184423898845</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -844,7 +778,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-FC1C-4AEC-B443-B10EF01652E3}"/>
+              <c16:uniqueId val="{00000000-9B5F-4800-A078-DAFD85A03BF7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -863,60 +797,19 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'5'!$K$4:$L$14</c:f>
-              <c:strCache>
-                <c:ptCount val="11"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.0001</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.0002</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.0003</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.0004</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.0005</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.0006</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.0007</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.0008</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.0009</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.001</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'5'!$J$4:$J$14</c:f>
+              <c:f>'5'!$R$22:$R$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-FC1C-4AEC-B443-B10EF01652E3}"/>
+              <c16:uniqueId val="{00000001-9B5F-4800-A078-DAFD85A03BF7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -929,17 +822,16 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1289711727"/>
-        <c:axId val="1289712143"/>
+        <c:axId val="829457119"/>
+        <c:axId val="829457535"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1289711727"/>
+        <c:axId val="829457119"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -976,7 +868,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1289712143"/>
+        <c:crossAx val="829457535"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -984,7 +876,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1289712143"/>
+        <c:axId val="829457535"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1035,7 +927,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1289711727"/>
+        <c:crossAx val="829457119"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2238,23 +2130,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>46566</xdr:rowOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>162983</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>560917</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>122766</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>412750</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>48683</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="10" name="Диаграмма 9">
+        <xdr:cNvPr id="2" name="Диаграмма 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{266CAE7B-9AC4-4BAC-B155-F79457510E64}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17A28EFE-4207-4CA0-8FDA-94B82F2EFE22}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2274,23 +2166,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>158750</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>264583</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>46566</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>513292</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>391583</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>122766</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="13" name="Диаграмма 12">
+        <xdr:cNvPr id="3" name="Диаграмма 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18B49F3E-EE74-4628-B590-B13ACDF32513}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23F90FCB-454D-4987-AF82-F28DA58910EC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2309,108 +2201,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Лист1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="44">
-          <cell r="M44">
-            <v>0</v>
-          </cell>
-          <cell r="O44">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="M45">
-            <v>9.9999999999999995E-8</v>
-          </cell>
-          <cell r="O45">
-            <v>0.22926961876825236</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="M46">
-            <v>1.9999999999999999E-7</v>
-          </cell>
-          <cell r="O46">
-            <v>0.40597467944636489</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="M47">
-            <v>2.9999999999999999E-7</v>
-          </cell>
-          <cell r="O47">
-            <v>0.54216663822838573</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="M48">
-            <v>3.9999999999999998E-7</v>
-          </cell>
-          <cell r="O48">
-            <v>0.6471339185411511</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="M49">
-            <v>4.9999999999999998E-7</v>
-          </cell>
-          <cell r="O49">
-            <v>0.72803539051346844</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="M50">
-            <v>5.9999999999999997E-7</v>
-          </cell>
-          <cell r="O50">
-            <v>0.79038861284890216</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="M51">
-            <v>6.9999999999999997E-7</v>
-          </cell>
-          <cell r="O51">
-            <v>0.83844613567051884</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="M52">
-            <v>7.9999999999999996E-7</v>
-          </cell>
-          <cell r="O52">
-            <v>0.87548552855587691</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="M53">
-            <v>8.9999999999999996E-7</v>
-          </cell>
-          <cell r="O53">
-            <v>0.90403291395500152</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="M54">
-            <v>9.9999999999999995E-7</v>
-          </cell>
-          <cell r="O54">
-            <v>0.92603525118683838</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2722,7 +2512,7 @@
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2" t="s">
@@ -2786,7 +2576,7 @@
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2" t="s">
@@ -2846,11 +2636,11 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2" t="s">
@@ -2909,11 +2699,11 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2" t="s">
@@ -2968,627 +2758,741 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{761E2066-09F1-4D2C-AF18-8AA8BCDB6B24}">
-  <dimension ref="A1:V29"/>
+  <dimension ref="A1:R33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="11" max="12" width="9.140625" style="1"/>
+    <col min="1" max="2" width="14" customWidth="1"/>
+    <col min="3" max="4" width="14" style="1" customWidth="1"/>
+    <col min="5" max="8" width="14" customWidth="1"/>
+    <col min="9" max="10" width="14" style="1" customWidth="1"/>
+    <col min="11" max="12" width="14" customWidth="1"/>
+    <col min="13" max="14" width="11.140625" customWidth="1"/>
+    <col min="15" max="16" width="11.140625" style="1" customWidth="1"/>
+    <col min="17" max="24" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="5" t="s">
+    <row r="1" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="14"/>
+      <c r="G1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="2" t="s">
+      <c r="H1" s="13"/>
+      <c r="I1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="3"/>
+      <c r="O1" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="3"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>5000000</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3">
+        <f>158*8</f>
+        <v>1264</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3">
+        <f>A3/E3</f>
+        <v>3955.6962025316457</v>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3">
+        <f>C3/3600</f>
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3">
+        <f>I3*(180/0.01)</f>
+        <v>5000</v>
+      </c>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3">
+        <f>K3/G3</f>
+        <v>1.264</v>
+      </c>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3">
+        <f>1-EXP(1)^(-$G$3*(1-$M$3)*O3)</f>
+        <v>0</v>
+      </c>
+      <c r="R3" s="3"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="I4"/>
+      <c r="J4"/>
+      <c r="O4" s="3">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3">
+        <f t="shared" ref="Q4:Q14" si="0">1-EXP(1)^(-$G$3*(1-$M$3)*O4)</f>
+        <v>-1.0497756806822744E-2</v>
+      </c>
+      <c r="R4" s="3"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="I5"/>
+      <c r="J5"/>
+      <c r="O5" s="11">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="3">
+        <f t="shared" si="0"/>
+        <v>-2.1105716511620631E-2</v>
+      </c>
+      <c r="R5" s="3"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="O6" s="11">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="3">
+        <f t="shared" si="0"/>
+        <v>-3.1825035997616213E-2</v>
+      </c>
+      <c r="R6" s="3"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C7"/>
+      <c r="D7"/>
+      <c r="I7"/>
+      <c r="J7"/>
+      <c r="O7" s="11">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="3">
+        <f t="shared" si="0"/>
+        <v>-4.2656884292710195E-2</v>
+      </c>
+      <c r="R7" s="3"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C8"/>
+      <c r="D8"/>
+      <c r="I8"/>
+      <c r="J8"/>
+      <c r="O8" s="11">
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="3">
+        <f t="shared" si="0"/>
+        <v>-5.3602442696974562E-2</v>
+      </c>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C9"/>
+      <c r="D9"/>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="O9" s="11">
+        <v>6.0000000000000002E-5</v>
+      </c>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="3">
+        <f t="shared" si="0"/>
+        <v>-6.4662904911481744E-2</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="I10"/>
+      <c r="J10"/>
+      <c r="O10" s="11">
+        <v>6.9999999999999994E-5</v>
+      </c>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="3">
+        <f t="shared" si="0"/>
+        <v>-7.5839477168488045E-2</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C11"/>
+      <c r="D11"/>
+      <c r="I11"/>
+      <c r="J11"/>
+      <c r="O11" s="11">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="3">
+        <f t="shared" si="0"/>
+        <v>-8.7133378362982183E-2</v>
+      </c>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="I12"/>
+      <c r="J12"/>
+      <c r="O12" s="11">
+        <v>1E-4</v>
+      </c>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="3">
+        <f t="shared" si="0"/>
+        <v>-0.1100781072570316</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="I13"/>
+      <c r="J13"/>
+      <c r="O13" s="11">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="3">
+        <f t="shared" si="0"/>
+        <v>-0.2322734042113539</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C14"/>
+      <c r="D14"/>
+      <c r="I14"/>
+      <c r="J14"/>
+      <c r="O14" s="11">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="3">
+        <f t="shared" si="0"/>
+        <v>-0.36791972817011875</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C15"/>
+      <c r="D15"/>
+      <c r="I15"/>
+      <c r="J15"/>
+      <c r="O15"/>
+      <c r="P15"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C16"/>
+      <c r="D16"/>
+      <c r="I16"/>
+      <c r="J16"/>
+      <c r="O16"/>
+      <c r="P16"/>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C17"/>
+      <c r="D17"/>
+      <c r="I17"/>
+      <c r="J17"/>
+      <c r="O17"/>
+      <c r="P17"/>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C18"/>
+      <c r="D18"/>
+      <c r="I18"/>
+      <c r="J18"/>
+      <c r="O18"/>
+      <c r="P18"/>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C19"/>
+      <c r="D19"/>
+      <c r="I19"/>
+      <c r="J19"/>
+      <c r="O19"/>
+      <c r="P19"/>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2" t="s">
+      <c r="B20" s="13"/>
+      <c r="C20" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="14"/>
+      <c r="G20" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="13"/>
+      <c r="I20" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="2"/>
-      <c r="K1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="6"/>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="8"/>
-      <c r="V2">
-        <f>1</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="10"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
-        <v>1</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="11">
-        <v>1264</v>
-      </c>
-      <c r="D4" s="12"/>
-      <c r="E4" s="3">
+      <c r="J20" s="3"/>
+      <c r="K20" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N20" s="3"/>
+      <c r="O20" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="P20" s="13"/>
+      <c r="Q20" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="13"/>
+      <c r="P21" s="13"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
         <v>5000000</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="15">
-        <f>E4/C4</f>
-        <v>3955.6962025316457</v>
-      </c>
-      <c r="H4" s="15"/>
-      <c r="I4" s="3">
-        <f>1 -EXP(1)^(-G$4*K4)</f>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3">
+        <f>318*8</f>
+        <v>2544</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3">
+        <f>A22/E22</f>
+        <v>1965.4088050314465</v>
+      </c>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3">
+        <f>C22/3600</f>
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3">
+        <f>I22*(180/0.03)</f>
+        <v>1666.6666666666667</v>
+      </c>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3">
+        <f>K22/G22</f>
+        <v>0.84800000000000009</v>
+      </c>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="13">
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3">
+        <f>1-EXP(1)^(-$G$22*(1-$M$22)*O22)</f>
         <v>0</v>
       </c>
-      <c r="L4" s="14"/>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="3">
-        <f t="shared" ref="I5:I14" si="0">1 -EXP(1)^(-G$4*K5)</f>
-        <v>0.32670359327284115</v>
-      </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="16">
-        <v>1E-4</v>
-      </c>
-      <c r="L5" s="17"/>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="3">
-        <f t="shared" si="0"/>
-        <v>0.54667194868829627</v>
-      </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="16">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="L6" s="17"/>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="3">
-        <f t="shared" si="0"/>
-        <v>0.6947758519832048</v>
-      </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="16">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="L7" s="17"/>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="3">
-        <f t="shared" si="0"/>
-        <v>0.79449367789393333</v>
-      </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="16">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="L8" s="17"/>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="3">
-        <f t="shared" si="0"/>
-        <v>0.86163333176627122</v>
-      </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="16">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="L9" s="17"/>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="3">
-        <f t="shared" si="0"/>
-        <v>0.90683821946742149</v>
-      </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="16">
-        <v>5.9999999999999995E-4</v>
-      </c>
-      <c r="L10" s="17"/>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="3">
-        <f t="shared" si="0"/>
-        <v>0.93727450792311073</v>
-      </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="16">
-        <v>6.9999999999999999E-4</v>
-      </c>
-      <c r="L11" s="17"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="3">
-        <f t="shared" si="0"/>
-        <v>0.95776715157443759</v>
-      </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="16">
-        <v>8.0000000000000004E-4</v>
-      </c>
-      <c r="L12" s="17"/>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="3">
-        <f t="shared" si="0"/>
-        <v>0.97156477490921611</v>
-      </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="16">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="L13" s="17"/>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="3">
-        <f t="shared" si="0"/>
-        <v>0.98085466512189723</v>
-      </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="18">
-        <v>1E-3</v>
-      </c>
-      <c r="L14" s="19"/>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J16" s="2"/>
-      <c r="K16" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="L16" s="6"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="8"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="10"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
-        <v>2</v>
-      </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="11">
-        <f>2544</f>
-        <v>2544</v>
-      </c>
-      <c r="D19" s="12"/>
-      <c r="E19" s="3">
-        <v>5000000</v>
-      </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="15">
-        <f>(E19/C19)</f>
-        <v>1965.4088050314465</v>
-      </c>
-      <c r="H19" s="15"/>
-      <c r="I19" s="3">
-        <f>1 -EXP(1)^(-G$19*K19)</f>
-        <v>0</v>
-      </c>
-      <c r="J19" s="3"/>
-      <c r="K19" s="13">
-        <v>0</v>
-      </c>
-      <c r="L19" s="14"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="3">
-        <f t="shared" ref="I20:I29" si="1">1 -EXP(1)^(-G$19*K20)</f>
-        <v>0.17843225549402686</v>
-      </c>
-      <c r="J20" s="3"/>
-      <c r="K20" s="16">
-        <v>1E-4</v>
-      </c>
-      <c r="L20" s="17"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="3">
-        <f t="shared" si="1"/>
-        <v>0.32502644118736801</v>
-      </c>
-      <c r="J21" s="3"/>
-      <c r="K21" s="16">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="L21" s="17"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="3">
-        <f t="shared" si="1"/>
-        <v>0.4454634956851361</v>
-      </c>
-      <c r="J22" s="3"/>
-      <c r="K22" s="16">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="L22" s="17"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
-      <c r="I23" s="3">
-        <f t="shared" si="1"/>
-        <v>0.54441069490381055</v>
-      </c>
-      <c r="J23" s="3"/>
-      <c r="K23" s="16">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="L23" s="17"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="3">
+        <v>1E-3</v>
+      </c>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3">
+        <f t="shared" ref="Q23:Q33" si="1">1-EXP(1)^(-$G$22*(1-$M$22)*O23)</f>
+        <v>0.25824934618682516</v>
+      </c>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="20"/>
+      <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
-      <c r="I24" s="3">
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="11">
+        <v>2E-3</v>
+      </c>
+      <c r="P24" s="12"/>
+      <c r="Q24" s="3">
         <f t="shared" si="1"/>
-        <v>0.62570252219107991</v>
-      </c>
-      <c r="J24" s="3"/>
-      <c r="K24" s="16">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="L24" s="17"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0.44980596756772784</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
-      <c r="I25" s="3">
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="11">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="P25" s="12"/>
+      <c r="Q25" s="3">
         <f t="shared" si="1"/>
-        <v>0.69248926538225097</v>
-      </c>
-      <c r="J25" s="3"/>
-      <c r="K25" s="16">
-        <v>5.9999999999999995E-4</v>
-      </c>
-      <c r="L25" s="17"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0.59189321671925499</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
-      <c r="I26" s="3">
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="11">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="P26" s="12"/>
+      <c r="Q26" s="3">
         <f t="shared" si="1"/>
-        <v>0.74735909934872113</v>
-      </c>
-      <c r="J26" s="3"/>
-      <c r="K26" s="16">
-        <v>6.9999999999999999E-4</v>
-      </c>
-      <c r="L26" s="17"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0.69728652667591584</v>
+      </c>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
-      <c r="I27" s="3">
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="11">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="P27" s="12"/>
+      <c r="Q27" s="3">
         <f t="shared" si="1"/>
-        <v>0.79243838508197117</v>
-      </c>
-      <c r="J27" s="3"/>
-      <c r="K27" s="16">
-        <v>8.0000000000000004E-4</v>
-      </c>
-      <c r="L27" s="17"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0.7754620832438035</v>
+      </c>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
-      <c r="I28" s="3">
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="11">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="P28" s="12"/>
+      <c r="Q28" s="3">
         <f t="shared" si="1"/>
-        <v>0.82947407218577773</v>
-      </c>
-      <c r="J28" s="3"/>
-      <c r="K28" s="16">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="L28" s="17"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0.833448853440243</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
-      <c r="I29" s="3">
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="11">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="P29" s="12"/>
+      <c r="Q29" s="3">
         <f t="shared" si="1"/>
-        <v>0.85990139810588095</v>
-      </c>
-      <c r="J29" s="3"/>
-      <c r="K29" s="18">
-        <v>1E-3</v>
-      </c>
-      <c r="L29" s="19"/>
+        <v>0.87646057814596645</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="11">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="P30" s="12"/>
+      <c r="Q30" s="3">
+        <f t="shared" si="1"/>
+        <v>0.90836455306806896</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="11">
+        <v>0.01</v>
+      </c>
+      <c r="P31" s="12"/>
+      <c r="Q31" s="3">
+        <f t="shared" si="1"/>
+        <v>0.9495827239387874</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="11">
+        <v>0.02</v>
+      </c>
+      <c r="P32" s="12"/>
+      <c r="Q32" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99745809827456744</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="11">
+        <v>0.03</v>
+      </c>
+      <c r="P33" s="12"/>
+      <c r="Q33" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99987184423898845</v>
+      </c>
+      <c r="R33" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="64">
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="K29:L29"/>
-    <mergeCell ref="K21:L21"/>
+  <mergeCells count="80">
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="Q32:R32"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="Q33:R33"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="Q30:R30"/>
     <mergeCell ref="K22:L22"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="K16:L18"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="K1:L3"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="I1:J3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="A1:B3"/>
-    <mergeCell ref="C1:D3"/>
-    <mergeCell ref="E1:F3"/>
-    <mergeCell ref="G1:H3"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="A16:B18"/>
-    <mergeCell ref="C16:D18"/>
-    <mergeCell ref="E16:F18"/>
-    <mergeCell ref="G16:H18"/>
-    <mergeCell ref="I16:J18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="Q22:R22"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:H22"/>
     <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="Q14:R14"/>
+    <mergeCell ref="A20:B21"/>
+    <mergeCell ref="C20:D21"/>
+    <mergeCell ref="E20:F21"/>
+    <mergeCell ref="G20:H21"/>
+    <mergeCell ref="I20:J21"/>
+    <mergeCell ref="K20:L21"/>
+    <mergeCell ref="M20:N21"/>
+    <mergeCell ref="O20:P21"/>
+    <mergeCell ref="Q20:R21"/>
+    <mergeCell ref="Q9:R9"/>
+    <mergeCell ref="Q10:R10"/>
+    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="Q12:R12"/>
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="Q5:R5"/>
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="Q8:R8"/>
+    <mergeCell ref="M1:N2"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="O1:P2"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="Q1:R2"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="I1:J2"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K1:L2"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="C1:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E1:F2"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="G1:H2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="O9:P9"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="O12:P12"/>
+    <mergeCell ref="O13:P13"/>
+    <mergeCell ref="O14:P14"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="O22:P22"/>
+    <mergeCell ref="O23:P23"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="O25:P25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/Кибер физ/3 лаба в методичке 7 лаба.xlsx
+++ b/Кибер физ/3 лаба в методичке 7 лаба.xlsx
@@ -5,19 +5,20 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\study\works\Кибер физ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programs\Programs\Study\Кибер физ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A97693-F9EE-40A5-9F76-A8EA5B7E2658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D86A8B-9750-4A9C-8B77-AE66B0B13EE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="4" xr2:uid="{204A04D1-E1E4-4B3D-A404-03DEBDA79D09}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14160" activeTab="4" xr2:uid="{204A04D1-E1E4-4B3D-A404-03DEBDA79D09}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId1"/>
     <sheet name="2" sheetId="2" r:id="rId2"/>
     <sheet name="3" sheetId="3" r:id="rId3"/>
     <sheet name="4" sheetId="4" r:id="rId4"/>
-    <sheet name="5" sheetId="5" r:id="rId5"/>
+    <sheet name="Лист1" sheetId="6" r:id="rId5"/>
+    <sheet name="5" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="23">
   <si>
     <t>Время формирования пакета, с</t>
   </si>
@@ -87,6 +88,27 @@
   <si>
     <t>ФРБ</t>
   </si>
+  <si>
+    <t>tcod, c</t>
+  </si>
+  <si>
+    <t>ts, c</t>
+  </si>
+  <si>
+    <t>lam pac, пакетов/в час</t>
+  </si>
+  <si>
+    <t>скорость v, байт в секунду</t>
+  </si>
+  <si>
+    <t>u, за одну секунду</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>H(t)</t>
+  </si>
 </sst>
 </file>
 
@@ -112,7 +134,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -223,11 +245,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -269,6 +317,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -287,6 +355,796 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>H(t)</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>№1</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$P$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>H(t)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Лист1!$O$2:$O$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1E-4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.0000000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.9999999999999997E-4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.0000000000000002E-4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.0000000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5.9999999999999995E-4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.9999999999999999E-4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8.0000000000000004E-4</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8.9999999999999998E-4</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Лист1!$P$2:$P$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.32670359327284115</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.54667194868829627</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.6947758519832048</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.79449367789393333</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.86163333176627122</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.90683821946742149</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.93727450792311073</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.95776715157443759</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.97156477490921611</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.98085466512189723</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.99963345615240529</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-60BB-4B0B-A02B-D65B36484F13}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1321215856"/>
+        <c:axId val="1321213776"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1321215856"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1321213776"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1321213776"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1321215856"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>H(t)</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>№2</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$P$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>H(t)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Лист1!$O$21:$O$33</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1E-4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.0000000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.9999999999999997E-4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.0000000000000002E-4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.0000000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5.9999999999999995E-4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.9999999999999999E-4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8.0000000000000004E-4</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8.9999999999999998E-4</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Лист1!$P$21:$P$33</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.17843225549402686</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.32502644118736801</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.4454634956851361</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.54441069490381055</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.62570252219107991</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.69248926538225097</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.74735909934872113</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.79243838508197117</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.82947407218577773</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.85990139810588095</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.98037238174731312</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-813B-4733-BDE5-A12F5679BAA3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="833327552"/>
+        <c:axId val="833326304"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="833327552"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="833326304"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="833326304"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="833327552"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
@@ -635,7 +1493,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
@@ -730,6 +1588,50 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'5'!$O$22:$P$33</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0,001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0,002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0,003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0,004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0,005</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0,006</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0,007</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0,008</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0,01</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0,02</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0,03</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
           <c:val>
             <c:numRef>
               <c:f>'5'!$Q$22:$Q$33</c:f>
@@ -797,6 +1699,50 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'5'!$O$22:$P$33</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0,001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0,002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0,003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0,004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0,005</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0,006</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0,007</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0,008</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0,01</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0,02</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0,03</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
           <c:val>
             <c:numRef>
               <c:f>'5'!$R$22:$R$33</c:f>
@@ -832,6 +1778,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1094,8 +2041,88 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -1122,8 +2149,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -1203,11 +2230,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -1218,11 +2240,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -1234,7 +2251,7 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+      <a:ln w="19050" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -1254,9 +2271,6 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1269,10 +2283,10 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -1312,22 +2326,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -1432,8 +2447,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -1565,19 +2580,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -1591,6 +2607,17 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -1611,7 +2638,7 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -1638,8 +2665,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -1719,11 +2746,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -1734,11 +2756,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -1750,7 +2767,7 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+      <a:ln w="19050" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -1770,6 +2787,532 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="phClr"/>
       </a:solidFill>
@@ -2126,7 +3669,683 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>700216</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>144162</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>666727</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>164039</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Рисунок 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDDC6763-F241-4A39-841D-5F30009901BD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11234351" y="885567"/>
+          <a:ext cx="1686160" cy="390580"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>700216</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>144162</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1686160" cy="390580"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Рисунок 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65628852-BC33-4EB1-8E4C-827F3EC026C2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11234351" y="885567"/>
+          <a:ext cx="1686160" cy="390580"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>370703</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>90616</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>370703</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>53546</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="Диаграмма 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3DCCC0D0-EF03-4A28-A945-E0CBF04FE093}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>463379</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>28833</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>463379</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>177114</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="10" name="Диаграмма 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8775996-5363-4D04-B018-F12A665D2A68}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -2501,12 +4720,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77B7DAC2-207E-4AE8-A7E1-2858C9154FE5}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2520,7 +4739,7 @@
       </c>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2528,7 +4747,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -2536,7 +4755,7 @@
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>0.03</v>
       </c>
@@ -2568,9 +4787,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9278F117-773C-4783-921E-F2602F09A077}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2584,7 +4803,7 @@
       </c>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2592,7 +4811,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -2600,7 +4819,7 @@
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>0.01</v>
       </c>
@@ -2632,9 +4851,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20B9C12A-C057-4661-8314-CF59A6C20DCA}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>5</v>
       </c>
@@ -2648,7 +4867,7 @@
       </c>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="2"/>
@@ -2656,7 +4875,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
       <c r="B3" s="10"/>
       <c r="C3" s="2"/>
@@ -2664,7 +4883,7 @@
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
         <v>1264</v>
       </c>
@@ -2695,9 +4914,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323FE3B6-40B0-46B1-9562-61B140DB775B}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>5</v>
       </c>
@@ -2711,7 +4930,7 @@
       </c>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="2"/>
@@ -2719,7 +4938,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
       <c r="B3" s="10"/>
       <c r="C3" s="2"/>
@@ -2727,7 +4946,7 @@
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
         <f>2544</f>
         <v>2544</v>
@@ -2757,21 +4976,459 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B926B8AA-0754-4128-82D8-01970B8FC902}">
+  <dimension ref="A1:W33"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="12" width="14" style="1" customWidth="1"/>
+    <col min="13" max="22" width="11.109375" style="1" customWidth="1"/>
+    <col min="23" max="23" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="14"/>
+      <c r="G1" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="13"/>
+      <c r="I1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N1" s="3"/>
+      <c r="O1" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="P1" s="21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="18"/>
+      <c r="P2" s="22"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3">
+        <f>3*60</f>
+        <v>180</v>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3">
+        <f>E3*(G3/A3)</f>
+        <v>18000</v>
+      </c>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3">
+        <f>5*10^6/8</f>
+        <v>625000</v>
+      </c>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3">
+        <f>K3/158</f>
+        <v>3955.6962025316457</v>
+      </c>
+      <c r="N3" s="3"/>
+      <c r="O3" s="16">
+        <v>0</v>
+      </c>
+      <c r="P3" s="16">
+        <f>1-EXP(1)^(-($M$3*O3))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O4" s="16">
+        <v>1E-4</v>
+      </c>
+      <c r="P4" s="16">
+        <f t="shared" ref="P4:P14" si="0">1-EXP(1)^(-($M$3*O4))</f>
+        <v>0.32670359327284115</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O5" s="15">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="P5" s="16">
+        <f t="shared" si="0"/>
+        <v>0.54667194868829627</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O6" s="15">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="P6" s="16">
+        <f t="shared" si="0"/>
+        <v>0.6947758519832048</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O7" s="15">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="P7" s="16">
+        <f t="shared" si="0"/>
+        <v>0.79449367789393333</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O8" s="15">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="P8" s="16">
+        <f t="shared" si="0"/>
+        <v>0.86163333176627122</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O9" s="15">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="P9" s="16">
+        <f t="shared" si="0"/>
+        <v>0.90683821946742149</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O10" s="15">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="P10" s="16">
+        <f t="shared" si="0"/>
+        <v>0.93727450792311073</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O11" s="15">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="P11" s="16">
+        <f t="shared" si="0"/>
+        <v>0.95776715157443759</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O12" s="15">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="P12" s="16">
+        <f t="shared" si="0"/>
+        <v>0.97156477490921611</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O13" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="P13" s="16">
+        <f t="shared" si="0"/>
+        <v>0.98085466512189723</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O14" s="15">
+        <v>2E-3</v>
+      </c>
+      <c r="P14" s="16">
+        <f t="shared" si="0"/>
+        <v>0.99963345615240529</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A20" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="13"/>
+      <c r="C20" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="14"/>
+      <c r="G20" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="H20" s="13"/>
+      <c r="I20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N20" s="3"/>
+      <c r="O20" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="P20" s="19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="18"/>
+      <c r="P21" s="20"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <v>0.03</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3">
+        <v>1</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3">
+        <f>3*60</f>
+        <v>180</v>
+      </c>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3">
+        <f>E22*(G22/A22)</f>
+        <v>6000</v>
+      </c>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3">
+        <f>5*10^6/8</f>
+        <v>625000</v>
+      </c>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3">
+        <f>K22/318</f>
+        <v>1965.4088050314465</v>
+      </c>
+      <c r="N22" s="3"/>
+      <c r="O22" s="16">
+        <v>0</v>
+      </c>
+      <c r="P22" s="16">
+        <f>1-EXP(1)^(-($M$22*O22))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O23" s="16">
+        <v>1E-4</v>
+      </c>
+      <c r="P23" s="16">
+        <f t="shared" ref="P23:P33" si="1">1-EXP(1)^(-($M$22*O23))</f>
+        <v>0.17843225549402686</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O24" s="15">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="P24" s="16">
+        <f t="shared" si="1"/>
+        <v>0.32502644118736801</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O25" s="15">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="P25" s="16">
+        <f t="shared" si="1"/>
+        <v>0.4454634956851361</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O26" s="15">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="P26" s="16">
+        <f t="shared" si="1"/>
+        <v>0.54441069490381055</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O27" s="15">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="P27" s="16">
+        <f t="shared" si="1"/>
+        <v>0.62570252219107991</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O28" s="15">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="P28" s="16">
+        <f t="shared" si="1"/>
+        <v>0.69248926538225097</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O29" s="15">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="P29" s="16">
+        <f t="shared" si="1"/>
+        <v>0.74735909934872113</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O30" s="15">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="P30" s="16">
+        <f t="shared" si="1"/>
+        <v>0.79243838508197117</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O31" s="15">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="P31" s="16">
+        <f t="shared" si="1"/>
+        <v>0.82947407218577773</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O32" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="P32" s="16">
+        <f t="shared" si="1"/>
+        <v>0.85990139810588095</v>
+      </c>
+    </row>
+    <row r="33" spans="15:16" x14ac:dyDescent="0.3">
+      <c r="O33" s="15">
+        <v>2E-3</v>
+      </c>
+      <c r="P33" s="16">
+        <f t="shared" si="1"/>
+        <v>0.98037238174731312</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="32">
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+    <mergeCell ref="O20:O21"/>
+    <mergeCell ref="P20:P21"/>
+    <mergeCell ref="M20:N21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="A20:B21"/>
+    <mergeCell ref="C20:D21"/>
+    <mergeCell ref="E20:F21"/>
+    <mergeCell ref="G20:H21"/>
+    <mergeCell ref="I20:J21"/>
+    <mergeCell ref="K20:L21"/>
+    <mergeCell ref="M1:N2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:D2"/>
+    <mergeCell ref="E1:F2"/>
+    <mergeCell ref="G1:H2"/>
+    <mergeCell ref="I1:J2"/>
+    <mergeCell ref="K1:L2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{761E2066-09F1-4D2C-AF18-8AA8BCDB6B24}">
   <dimension ref="A1:R33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
     <col min="3" max="4" width="14" style="1" customWidth="1"/>
     <col min="5" max="8" width="14" customWidth="1"/>
     <col min="9" max="10" width="14" style="1" customWidth="1"/>
     <col min="11" max="12" width="14" customWidth="1"/>
-    <col min="13" max="14" width="11.140625" customWidth="1"/>
-    <col min="15" max="16" width="11.140625" style="1" customWidth="1"/>
-    <col min="17" max="24" width="11.140625" customWidth="1"/>
+    <col min="13" max="14" width="11.109375" customWidth="1"/>
+    <col min="15" max="16" width="11.109375" style="1" customWidth="1"/>
+    <col min="17" max="24" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
         <v>10</v>
       </c>
@@ -2809,7 +5466,7 @@
       </c>
       <c r="R1" s="3"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="13"/>
       <c r="B2" s="13"/>
       <c r="C2" s="14"/>
@@ -2829,7 +5486,7 @@
       <c r="Q2" s="3"/>
       <c r="R2" s="3"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>5000000</v>
       </c>
@@ -2873,7 +5530,7 @@
       </c>
       <c r="R3" s="3"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C4"/>
       <c r="D4"/>
       <c r="I4"/>
@@ -2888,7 +5545,7 @@
       </c>
       <c r="R4" s="3"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C5"/>
       <c r="D5"/>
       <c r="I5"/>
@@ -2903,7 +5560,7 @@
       </c>
       <c r="R5" s="3"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C6"/>
       <c r="D6"/>
       <c r="I6"/>
@@ -2918,7 +5575,7 @@
       </c>
       <c r="R6" s="3"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C7"/>
       <c r="D7"/>
       <c r="I7"/>
@@ -2933,7 +5590,7 @@
       </c>
       <c r="R7" s="3"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C8"/>
       <c r="D8"/>
       <c r="I8"/>
@@ -2948,7 +5605,7 @@
       </c>
       <c r="R8" s="3"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C9"/>
       <c r="D9"/>
       <c r="I9"/>
@@ -2963,7 +5620,7 @@
       </c>
       <c r="R9" s="3"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C10"/>
       <c r="D10"/>
       <c r="I10"/>
@@ -2978,7 +5635,7 @@
       </c>
       <c r="R10" s="3"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C11"/>
       <c r="D11"/>
       <c r="I11"/>
@@ -2993,7 +5650,7 @@
       </c>
       <c r="R11" s="3"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C12"/>
       <c r="D12"/>
       <c r="I12"/>
@@ -3008,7 +5665,7 @@
       </c>
       <c r="R12" s="3"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C13"/>
       <c r="D13"/>
       <c r="I13"/>
@@ -3023,7 +5680,7 @@
       </c>
       <c r="R13" s="3"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C14"/>
       <c r="D14"/>
       <c r="I14"/>
@@ -3038,7 +5695,7 @@
       </c>
       <c r="R14" s="3"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C15"/>
       <c r="D15"/>
       <c r="I15"/>
@@ -3046,7 +5703,7 @@
       <c r="O15"/>
       <c r="P15"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C16"/>
       <c r="D16"/>
       <c r="I16"/>
@@ -3054,7 +5711,7 @@
       <c r="O16"/>
       <c r="P16"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C17"/>
       <c r="D17"/>
       <c r="I17"/>
@@ -3062,7 +5719,7 @@
       <c r="O17"/>
       <c r="P17"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C18"/>
       <c r="D18"/>
       <c r="I18"/>
@@ -3070,7 +5727,7 @@
       <c r="O18"/>
       <c r="P18"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C19"/>
       <c r="D19"/>
       <c r="I19"/>
@@ -3078,7 +5735,7 @@
       <c r="O19"/>
       <c r="P19"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
         <v>10</v>
       </c>
@@ -3116,7 +5773,7 @@
       </c>
       <c r="R20" s="3"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>
       <c r="B21" s="13"/>
       <c r="C21" s="14"/>
@@ -3136,7 +5793,7 @@
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>5000000</v>
       </c>
@@ -3180,7 +5837,7 @@
       </c>
       <c r="R22" s="3"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="E23" s="1"/>
@@ -3201,7 +5858,7 @@
       </c>
       <c r="R23" s="3"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="E24" s="1"/>
@@ -3222,7 +5879,7 @@
       </c>
       <c r="R24" s="3"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="E25" s="1"/>
@@ -3243,7 +5900,7 @@
       </c>
       <c r="R25" s="3"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="E26" s="1"/>
@@ -3264,7 +5921,7 @@
       </c>
       <c r="R26" s="3"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="E27" s="1"/>
@@ -3285,7 +5942,7 @@
       </c>
       <c r="R27" s="3"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="E28" s="1"/>
@@ -3306,7 +5963,7 @@
       </c>
       <c r="R28" s="3"/>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="E29" s="1"/>
@@ -3327,7 +5984,7 @@
       </c>
       <c r="R29" s="3"/>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="E30" s="1"/>
@@ -3348,7 +6005,7 @@
       </c>
       <c r="R30" s="3"/>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="E31" s="1"/>
@@ -3369,7 +6026,7 @@
       </c>
       <c r="R31" s="3"/>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="E32" s="1"/>
@@ -3390,7 +6047,7 @@
       </c>
       <c r="R32" s="3"/>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="E33" s="1"/>
@@ -3425,16 +6082,28 @@
     <mergeCell ref="Q29:R29"/>
     <mergeCell ref="O30:P30"/>
     <mergeCell ref="Q30:R30"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="O29:P29"/>
     <mergeCell ref="K22:L22"/>
     <mergeCell ref="Q22:R22"/>
     <mergeCell ref="Q23:R23"/>
     <mergeCell ref="Q24:R24"/>
     <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="O22:P22"/>
+    <mergeCell ref="O23:P23"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="O25:P25"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="E22:F22"/>
     <mergeCell ref="G22:H22"/>
     <mergeCell ref="I22:J22"/>
+    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="Q12:R12"/>
+    <mergeCell ref="Q13:R13"/>
     <mergeCell ref="Q14:R14"/>
     <mergeCell ref="A20:B21"/>
     <mergeCell ref="C20:D21"/>
@@ -3445,22 +6114,21 @@
     <mergeCell ref="M20:N21"/>
     <mergeCell ref="O20:P21"/>
     <mergeCell ref="Q20:R21"/>
-    <mergeCell ref="Q9:R9"/>
-    <mergeCell ref="Q10:R10"/>
-    <mergeCell ref="Q11:R11"/>
-    <mergeCell ref="Q12:R12"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="Q5:R5"/>
     <mergeCell ref="Q6:R6"/>
     <mergeCell ref="Q7:R7"/>
     <mergeCell ref="Q8:R8"/>
-    <mergeCell ref="M1:N2"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="O1:P2"/>
+    <mergeCell ref="Q9:R9"/>
+    <mergeCell ref="Q10:R10"/>
     <mergeCell ref="O3:P3"/>
     <mergeCell ref="Q1:R2"/>
     <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="Q5:R5"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="G1:H2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="O4:P4"/>
     <mergeCell ref="I1:J2"/>
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="K1:L2"/>
@@ -3469,12 +6137,9 @@
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="E1:F2"/>
     <mergeCell ref="E3:F3"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G1:H2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="M1:N2"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="O1:P2"/>
     <mergeCell ref="O5:P5"/>
     <mergeCell ref="O6:P6"/>
     <mergeCell ref="O7:P7"/>
@@ -3485,14 +6150,6 @@
     <mergeCell ref="O12:P12"/>
     <mergeCell ref="O13:P13"/>
     <mergeCell ref="O14:P14"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="O27:P27"/>
-    <mergeCell ref="O28:P28"/>
-    <mergeCell ref="O29:P29"/>
-    <mergeCell ref="O22:P22"/>
-    <mergeCell ref="O23:P23"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="O25:P25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/Кибер физ/3 лаба в методичке 7 лаба.xlsx
+++ b/Кибер физ/3 лаба в методичке 7 лаба.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programs\Programs\Study\Кибер физ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D86A8B-9750-4A9C-8B77-AE66B0B13EE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB383EFD-2C12-41EB-A42E-8B2475861A4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14160" activeTab="4" xr2:uid="{204A04D1-E1E4-4B3D-A404-03DEBDA79D09}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="24">
   <si>
     <t>Время формирования пакета, с</t>
   </si>
@@ -109,6 +109,9 @@
   <si>
     <t>H(t)</t>
   </si>
+  <si>
+    <t>a</t>
+  </si>
 </sst>
 </file>
 
@@ -134,7 +137,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -271,13 +274,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -311,14 +325,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -326,16 +332,28 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -527,37 +545,37 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.32670359327284115</c:v>
+                  <c:v>0.44524555881546557</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.54667194868829627</c:v>
+                  <c:v>0.69224750998603501</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.6947758519832048</c:v>
+                  <c:v>0.82927293937915381</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.79449367789393333</c:v>
+                  <c:v>0.90528840489020435</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.86163333176627122</c:v>
+                  <c:v>0.94745832198116942</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.90683821946742149</c:v>
+                  <c:v>0.97085227077176595</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.93727450792311073</c:v>
+                  <c:v>0.98383016776019283</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.95776715157443759</c:v>
+                  <c:v>0.99102971375175808</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.97156477490921611</c:v>
+                  <c:v>0.99502369386509126</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.98085466512189723</c:v>
+                  <c:v>0.99723937207096558</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.99963345615240529</c:v>
+                  <c:v>0.9999923789334374</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -922,37 +940,37 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.17843225549402686</c:v>
+                  <c:v>0.19696040572190809</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.32502644118736801</c:v>
+                  <c:v>0.35512741002167747</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.4454634956851361</c:v>
+                  <c:v>0.48214177698274563</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.54441069490381055</c:v>
+                  <c:v>0.5841393426946504</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.62570252219107991</c:v>
+                  <c:v>0.66604742648129145</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.69248926538225097</c:v>
+                  <c:v>0.73182286085341164</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.74735909934872113</c:v>
+                  <c:v>0.78464313898506433</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.79243838508197117</c:v>
+                  <c:v>0.82705991370556253</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.82947407218577773</c:v>
+                  <c:v>0.8611222632676967</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.85990139810588095</c:v>
+                  <c:v>0.88847567864023147</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.98037238174731312</c:v>
+                  <c:v>0.98756232574524305</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4342,6 +4360,50 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>616427</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>161519</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Рисунок 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{189A515E-0FA1-48B7-A6F6-89674061C921}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10510762" y="1632857"/>
+          <a:ext cx="2333951" cy="342948"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -4726,50 +4788,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="4"/>
+      <c r="E1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="2"/>
+      <c r="F1" s="4"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
+      <c r="A4" s="5">
         <v>0.03</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3">
+      <c r="B4" s="5"/>
+      <c r="C4" s="5">
         <f>158*8</f>
         <v>1264</v>
       </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="4">
+      <c r="D4" s="5"/>
+      <c r="E4" s="6">
         <f>C4/A4/1000</f>
         <v>42.133333333333333</v>
       </c>
-      <c r="F4" s="4"/>
+      <c r="F4" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -4790,50 +4852,50 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="4"/>
+      <c r="E1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="2"/>
+      <c r="F1" s="4"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
+      <c r="A4" s="5">
         <v>0.01</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3">
+      <c r="B4" s="5"/>
+      <c r="C4" s="5">
         <f>318*8</f>
         <v>2544</v>
       </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="4">
+      <c r="D4" s="5"/>
+      <c r="E4" s="6">
         <f>C4/A4/1000</f>
         <v>254.4</v>
       </c>
-      <c r="F4" s="4"/>
+      <c r="F4" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -4854,49 +4916,49 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="4"/>
+      <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2"/>
+      <c r="F1" s="4"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="9"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="9"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="A3" s="11"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="11">
+      <c r="A4" s="13">
         <v>1264</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="3">
+      <c r="B4" s="14"/>
+      <c r="C4" s="5">
         <v>5000000</v>
       </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="11">
+      <c r="D4" s="5"/>
+      <c r="E4" s="13">
         <f>A4/C4</f>
         <v>2.5280000000000002E-4</v>
       </c>
-      <c r="F4" s="12"/>
+      <c r="F4" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -4917,50 +4979,50 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="4"/>
+      <c r="E1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="2"/>
+      <c r="F1" s="4"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="9"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="9"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="A3" s="11"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="11">
+      <c r="A4" s="13">
         <f>2544</f>
         <v>2544</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="3">
+      <c r="B4" s="14"/>
+      <c r="C4" s="5">
         <v>5000000</v>
       </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="11">
+      <c r="D4" s="5"/>
+      <c r="E4" s="13">
         <f>A4/C4</f>
         <v>5.0880000000000001E-4</v>
       </c>
-      <c r="F4" s="12"/>
+      <c r="F4" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -4986,229 +5048,242 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="14" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14" t="s">
+      <c r="D1" s="22"/>
+      <c r="E1" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="14"/>
-      <c r="G1" s="13" t="s">
+      <c r="F1" s="22"/>
+      <c r="G1" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="13"/>
-      <c r="I1" s="3" t="s">
+      <c r="H1" s="21"/>
+      <c r="I1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3" t="s">
+      <c r="J1" s="5"/>
+      <c r="K1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3" t="s">
+      <c r="L1" s="5"/>
+      <c r="M1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="N1" s="3"/>
-      <c r="O1" s="17" t="s">
+      <c r="N1" s="5"/>
+      <c r="O1" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="P1" s="21" t="s">
+      <c r="P1" s="17" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="18"/>
-      <c r="P2" s="22"/>
+      <c r="A2" s="21"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="18"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
+      <c r="A3" s="5">
         <v>0.01</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5">
         <v>1000</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3">
+      <c r="D3" s="5"/>
+      <c r="E3" s="5">
         <v>1</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3">
+      <c r="F3" s="5"/>
+      <c r="G3" s="5">
         <f>3*60</f>
         <v>180</v>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3">
+      <c r="H3" s="5"/>
+      <c r="I3" s="5">
         <f>E3*(G3/A3)</f>
         <v>18000</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3">
+      <c r="J3" s="5"/>
+      <c r="K3" s="5">
         <f>5*10^6/8</f>
         <v>625000</v>
       </c>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3">
+      <c r="L3" s="5"/>
+      <c r="M3" s="5">
         <f>K3/158</f>
         <v>3955.6962025316457</v>
       </c>
-      <c r="N3" s="3"/>
-      <c r="O3" s="16">
+      <c r="N3" s="5"/>
+      <c r="O3" s="3">
         <v>0</v>
       </c>
-      <c r="P3" s="16">
-        <f>1-EXP(1)^(-($M$3*O3))</f>
+      <c r="P3" s="3">
+        <f>1-$I$5^(-($M$3*O3))</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="O4" s="16">
+      <c r="I4" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="24"/>
+      <c r="O4" s="3">
         <v>1E-4</v>
       </c>
-      <c r="P4" s="16">
-        <f t="shared" ref="P4:P14" si="0">1-EXP(1)^(-($M$3*O4))</f>
-        <v>0.32670359327284115</v>
+      <c r="P4" s="3">
+        <f t="shared" ref="P4:P14" si="0">1-$I$5^(-($M$3*O4))</f>
+        <v>0.44524555881546557</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="O5" s="15">
+      <c r="I5" s="23">
+        <f>I3*154/K3</f>
+        <v>4.4352</v>
+      </c>
+      <c r="J5" s="23"/>
+      <c r="O5" s="2">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="P5" s="16">
+      <c r="P5" s="3">
         <f t="shared" si="0"/>
-        <v>0.54667194868829627</v>
+        <v>0.69224750998603501</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="O6" s="15">
+      <c r="O6" s="2">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="P6" s="16">
+      <c r="P6" s="3">
         <f t="shared" si="0"/>
-        <v>0.6947758519832048</v>
+        <v>0.82927293937915381</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="O7" s="15">
+      <c r="O7" s="2">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="P7" s="16">
+      <c r="P7" s="3">
         <f t="shared" si="0"/>
-        <v>0.79449367789393333</v>
+        <v>0.90528840489020435</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="O8" s="15">
+      <c r="M8" s="1">
+        <f>1/M3</f>
+        <v>2.5280000000000002E-4</v>
+      </c>
+      <c r="O8" s="2">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="P8" s="16">
+      <c r="P8" s="3">
         <f t="shared" si="0"/>
-        <v>0.86163333176627122</v>
+        <v>0.94745832198116942</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="O9" s="15">
+      <c r="O9" s="2">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="P9" s="16">
+      <c r="P9" s="3">
         <f t="shared" si="0"/>
-        <v>0.90683821946742149</v>
+        <v>0.97085227077176595</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="O10" s="15">
+      <c r="O10" s="2">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="P10" s="16">
+      <c r="P10" s="3">
         <f t="shared" si="0"/>
-        <v>0.93727450792311073</v>
+        <v>0.98383016776019283</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="O11" s="15">
+      <c r="O11" s="2">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="P11" s="16">
+      <c r="P11" s="3">
         <f t="shared" si="0"/>
-        <v>0.95776715157443759</v>
+        <v>0.99102971375175808</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="O12" s="15">
+      <c r="O12" s="2">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="P12" s="16">
+      <c r="P12" s="3">
         <f t="shared" si="0"/>
-        <v>0.97156477490921611</v>
+        <v>0.99502369386509126</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="O13" s="15">
+      <c r="O13" s="2">
         <v>1E-3</v>
       </c>
-      <c r="P13" s="16">
+      <c r="P13" s="3">
         <f t="shared" si="0"/>
-        <v>0.98085466512189723</v>
+        <v>0.99723937207096558</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="O14" s="15">
+      <c r="O14" s="2">
         <v>2E-3</v>
       </c>
-      <c r="P14" s="16">
+      <c r="P14" s="3">
         <f t="shared" si="0"/>
-        <v>0.99963345615240529</v>
+        <v>0.9999923789334374</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="14" t="s">
+      <c r="B20" s="21"/>
+      <c r="C20" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14" t="s">
+      <c r="D20" s="22"/>
+      <c r="E20" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="F20" s="14"/>
-      <c r="G20" s="13" t="s">
+      <c r="F20" s="22"/>
+      <c r="G20" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="H20" s="13"/>
-      <c r="I20" s="3" t="s">
+      <c r="H20" s="21"/>
+      <c r="I20" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3" t="s">
+      <c r="J20" s="5"/>
+      <c r="K20" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3" t="s">
+      <c r="L20" s="5"/>
+      <c r="M20" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="N20" s="3"/>
-      <c r="O20" s="17" t="s">
+      <c r="N20" s="5"/>
+      <c r="O20" s="15" t="s">
         <v>21</v>
       </c>
       <c r="P20" s="19" t="s">
@@ -5216,175 +5291,186 @@
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="18"/>
+      <c r="A21" s="21"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="16"/>
       <c r="P21" s="20"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A22" s="3">
+      <c r="A22" s="5">
         <v>0.03</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3">
+      <c r="B22" s="5"/>
+      <c r="C22" s="5">
         <v>1000</v>
       </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3">
+      <c r="D22" s="5"/>
+      <c r="E22" s="5">
         <v>1</v>
       </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3">
+      <c r="F22" s="5"/>
+      <c r="G22" s="5">
         <f>3*60</f>
         <v>180</v>
       </c>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3">
+      <c r="H22" s="5"/>
+      <c r="I22" s="5">
         <f>E22*(G22/A22)</f>
         <v>6000</v>
       </c>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3">
+      <c r="J22" s="5"/>
+      <c r="K22" s="5">
         <f>5*10^6/8</f>
         <v>625000</v>
       </c>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3">
+      <c r="L22" s="5"/>
+      <c r="M22" s="5">
         <f>K22/318</f>
         <v>1965.4088050314465</v>
       </c>
-      <c r="N22" s="3"/>
-      <c r="O22" s="16">
+      <c r="N22" s="5"/>
+      <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="16">
-        <f>1-EXP(1)^(-($M$22*O22))</f>
+      <c r="P22" s="3">
+        <f>1-$I$24^(-($M$22*O22))</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="O23" s="16">
+      <c r="O23" s="3">
         <v>1E-4</v>
       </c>
-      <c r="P23" s="16">
-        <f t="shared" ref="P23:P33" si="1">1-EXP(1)^(-($M$22*O23))</f>
-        <v>0.17843225549402686</v>
+      <c r="P23" s="3">
+        <f t="shared" ref="P23:P33" si="1">1-$I$24^(-($M$22*O23))</f>
+        <v>0.19696040572190809</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="O24" s="15">
+      <c r="I24" s="23">
+        <f>I22*318/K22</f>
+        <v>3.0528</v>
+      </c>
+      <c r="J24" s="23"/>
+      <c r="O24" s="2">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="P24" s="16">
+      <c r="P24" s="3">
         <f t="shared" si="1"/>
-        <v>0.32502644118736801</v>
+        <v>0.35512741002167747</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="O25" s="15">
+      <c r="O25" s="2">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="P25" s="16">
+      <c r="P25" s="3">
         <f t="shared" si="1"/>
-        <v>0.4454634956851361</v>
+        <v>0.48214177698274563</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="O26" s="15">
+      <c r="O26" s="2">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="P26" s="16">
+      <c r="P26" s="3">
         <f t="shared" si="1"/>
-        <v>0.54441069490381055</v>
+        <v>0.5841393426946504</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="O27" s="15">
+      <c r="O27" s="2">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="P27" s="16">
+      <c r="P27" s="3">
         <f t="shared" si="1"/>
-        <v>0.62570252219107991</v>
+        <v>0.66604742648129145</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="O28" s="15">
+      <c r="O28" s="2">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="P28" s="16">
+      <c r="P28" s="3">
         <f t="shared" si="1"/>
-        <v>0.69248926538225097</v>
+        <v>0.73182286085341164</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="O29" s="15">
+      <c r="O29" s="2">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="P29" s="16">
+      <c r="P29" s="3">
         <f t="shared" si="1"/>
-        <v>0.74735909934872113</v>
+        <v>0.78464313898506433</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="O30" s="15">
+      <c r="O30" s="2">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="P30" s="16">
+      <c r="P30" s="3">
         <f t="shared" si="1"/>
-        <v>0.79243838508197117</v>
+        <v>0.82705991370556253</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="O31" s="15">
+      <c r="O31" s="2">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="P31" s="16">
+      <c r="P31" s="3">
         <f t="shared" si="1"/>
-        <v>0.82947407218577773</v>
+        <v>0.8611222632676967</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="O32" s="15">
+      <c r="O32" s="2">
         <v>1E-3</v>
       </c>
-      <c r="P32" s="16">
+      <c r="P32" s="3">
         <f t="shared" si="1"/>
-        <v>0.85990139810588095</v>
+        <v>0.88847567864023147</v>
       </c>
     </row>
     <row r="33" spans="15:16" x14ac:dyDescent="0.3">
-      <c r="O33" s="15">
+      <c r="O33" s="2">
         <v>2E-3</v>
       </c>
-      <c r="P33" s="16">
+      <c r="P33" s="3">
         <f t="shared" si="1"/>
-        <v>0.98037238174731312</v>
+        <v>0.98756232574524305</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="O1:O2"/>
-    <mergeCell ref="P1:P2"/>
-    <mergeCell ref="O20:O21"/>
-    <mergeCell ref="P20:P21"/>
-    <mergeCell ref="M20:N21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="I22:J22"/>
+  <mergeCells count="35">
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:D2"/>
+    <mergeCell ref="E1:F2"/>
+    <mergeCell ref="G1:H2"/>
+    <mergeCell ref="I1:J2"/>
+    <mergeCell ref="K1:L2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
     <mergeCell ref="K22:L22"/>
     <mergeCell ref="M22:N22"/>
     <mergeCell ref="A20:B21"/>
@@ -5393,20 +5479,17 @@
     <mergeCell ref="G20:H21"/>
     <mergeCell ref="I20:J21"/>
     <mergeCell ref="K20:L21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+    <mergeCell ref="O20:O21"/>
+    <mergeCell ref="P20:P21"/>
+    <mergeCell ref="M20:N21"/>
     <mergeCell ref="M1:N2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:D2"/>
-    <mergeCell ref="E1:F2"/>
-    <mergeCell ref="G1:H2"/>
-    <mergeCell ref="I1:J2"/>
-    <mergeCell ref="K1:L2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -5429,271 +5512,271 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="14" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14" t="s">
+      <c r="D1" s="22"/>
+      <c r="E1" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="14"/>
-      <c r="G1" s="13" t="s">
+      <c r="F1" s="22"/>
+      <c r="G1" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="13"/>
-      <c r="I1" s="3" t="s">
+      <c r="H1" s="21"/>
+      <c r="I1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3" t="s">
+      <c r="J1" s="5"/>
+      <c r="K1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3" t="s">
+      <c r="L1" s="5"/>
+      <c r="M1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="3"/>
-      <c r="O1" s="13" t="s">
+      <c r="N1" s="5"/>
+      <c r="O1" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="3" t="s">
+      <c r="P1" s="21"/>
+      <c r="Q1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="3"/>
+      <c r="R1" s="5"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
+      <c r="A2" s="21"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="21"/>
+      <c r="P2" s="21"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
+      <c r="A3" s="5">
         <v>5000000</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5">
         <v>1000</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3">
+      <c r="D3" s="5"/>
+      <c r="E3" s="5">
         <f>158*8</f>
         <v>1264</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3">
+      <c r="F3" s="5"/>
+      <c r="G3" s="5">
         <f>A3/E3</f>
         <v>3955.6962025316457</v>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3">
+      <c r="H3" s="5"/>
+      <c r="I3" s="5">
         <f>C3/3600</f>
         <v>0.27777777777777779</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3">
+      <c r="J3" s="5"/>
+      <c r="K3" s="5">
         <f>I3*(180/0.01)</f>
         <v>5000</v>
       </c>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3">
+      <c r="L3" s="5"/>
+      <c r="M3" s="5">
         <f>K3/G3</f>
         <v>1.264</v>
       </c>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3">
+      <c r="N3" s="5"/>
+      <c r="O3" s="5">
         <v>0</v>
       </c>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3">
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5">
         <f>1-EXP(1)^(-$G$3*(1-$M$3)*O3)</f>
         <v>0</v>
       </c>
-      <c r="R3" s="3"/>
+      <c r="R3" s="5"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C4"/>
       <c r="D4"/>
       <c r="I4"/>
       <c r="J4"/>
-      <c r="O4" s="3">
+      <c r="O4" s="5">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3">
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5">
         <f t="shared" ref="Q4:Q14" si="0">1-EXP(1)^(-$G$3*(1-$M$3)*O4)</f>
         <v>-1.0497756806822744E-2</v>
       </c>
-      <c r="R4" s="3"/>
+      <c r="R4" s="5"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C5"/>
       <c r="D5"/>
       <c r="I5"/>
       <c r="J5"/>
-      <c r="O5" s="11">
+      <c r="O5" s="13">
         <v>2.0000000000000002E-5</v>
       </c>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="3">
+      <c r="P5" s="14"/>
+      <c r="Q5" s="5">
         <f t="shared" si="0"/>
         <v>-2.1105716511620631E-2</v>
       </c>
-      <c r="R5" s="3"/>
+      <c r="R5" s="5"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C6"/>
       <c r="D6"/>
       <c r="I6"/>
       <c r="J6"/>
-      <c r="O6" s="11">
+      <c r="O6" s="13">
         <v>3.0000000000000001E-5</v>
       </c>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="3">
+      <c r="P6" s="14"/>
+      <c r="Q6" s="5">
         <f t="shared" si="0"/>
         <v>-3.1825035997616213E-2</v>
       </c>
-      <c r="R6" s="3"/>
+      <c r="R6" s="5"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C7"/>
       <c r="D7"/>
       <c r="I7"/>
       <c r="J7"/>
-      <c r="O7" s="11">
+      <c r="O7" s="13">
         <v>4.0000000000000003E-5</v>
       </c>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="3">
+      <c r="P7" s="14"/>
+      <c r="Q7" s="5">
         <f t="shared" si="0"/>
         <v>-4.2656884292710195E-2</v>
       </c>
-      <c r="R7" s="3"/>
+      <c r="R7" s="5"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C8"/>
       <c r="D8"/>
       <c r="I8"/>
       <c r="J8"/>
-      <c r="O8" s="11">
+      <c r="O8" s="13">
         <v>5.0000000000000002E-5</v>
       </c>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="3">
+      <c r="P8" s="14"/>
+      <c r="Q8" s="5">
         <f t="shared" si="0"/>
         <v>-5.3602442696974562E-2</v>
       </c>
-      <c r="R8" s="3"/>
+      <c r="R8" s="5"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C9"/>
       <c r="D9"/>
       <c r="I9"/>
       <c r="J9"/>
-      <c r="O9" s="11">
+      <c r="O9" s="13">
         <v>6.0000000000000002E-5</v>
       </c>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="3">
+      <c r="P9" s="14"/>
+      <c r="Q9" s="5">
         <f t="shared" si="0"/>
         <v>-6.4662904911481744E-2</v>
       </c>
-      <c r="R9" s="3"/>
+      <c r="R9" s="5"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C10"/>
       <c r="D10"/>
       <c r="I10"/>
       <c r="J10"/>
-      <c r="O10" s="11">
+      <c r="O10" s="13">
         <v>6.9999999999999994E-5</v>
       </c>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="3">
+      <c r="P10" s="14"/>
+      <c r="Q10" s="5">
         <f t="shared" si="0"/>
         <v>-7.5839477168488045E-2</v>
       </c>
-      <c r="R10" s="3"/>
+      <c r="R10" s="5"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C11"/>
       <c r="D11"/>
       <c r="I11"/>
       <c r="J11"/>
-      <c r="O11" s="11">
+      <c r="O11" s="13">
         <v>8.0000000000000007E-5</v>
       </c>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="3">
+      <c r="P11" s="14"/>
+      <c r="Q11" s="5">
         <f t="shared" si="0"/>
         <v>-8.7133378362982183E-2</v>
       </c>
-      <c r="R11" s="3"/>
+      <c r="R11" s="5"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C12"/>
       <c r="D12"/>
       <c r="I12"/>
       <c r="J12"/>
-      <c r="O12" s="11">
+      <c r="O12" s="13">
         <v>1E-4</v>
       </c>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="3">
+      <c r="P12" s="14"/>
+      <c r="Q12" s="5">
         <f t="shared" si="0"/>
         <v>-0.1100781072570316</v>
       </c>
-      <c r="R12" s="3"/>
+      <c r="R12" s="5"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C13"/>
       <c r="D13"/>
       <c r="I13"/>
       <c r="J13"/>
-      <c r="O13" s="11">
+      <c r="O13" s="13">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="P13" s="12"/>
-      <c r="Q13" s="3">
+      <c r="P13" s="14"/>
+      <c r="Q13" s="5">
         <f t="shared" si="0"/>
         <v>-0.2322734042113539</v>
       </c>
-      <c r="R13" s="3"/>
+      <c r="R13" s="5"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C14"/>
       <c r="D14"/>
       <c r="I14"/>
       <c r="J14"/>
-      <c r="O14" s="11">
+      <c r="O14" s="13">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="P14" s="12"/>
-      <c r="Q14" s="3">
+      <c r="P14" s="14"/>
+      <c r="Q14" s="5">
         <f t="shared" si="0"/>
         <v>-0.36791972817011875</v>
       </c>
-      <c r="R14" s="3"/>
+      <c r="R14" s="5"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C15"/>
@@ -5736,106 +5819,106 @@
       <c r="P19"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="14" t="s">
+      <c r="B20" s="21"/>
+      <c r="C20" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14" t="s">
+      <c r="D20" s="22"/>
+      <c r="E20" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="F20" s="14"/>
-      <c r="G20" s="13" t="s">
+      <c r="F20" s="22"/>
+      <c r="G20" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="H20" s="13"/>
-      <c r="I20" s="3" t="s">
+      <c r="H20" s="21"/>
+      <c r="I20" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3" t="s">
+      <c r="J20" s="5"/>
+      <c r="K20" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3" t="s">
+      <c r="L20" s="5"/>
+      <c r="M20" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N20" s="3"/>
-      <c r="O20" s="13" t="s">
+      <c r="N20" s="5"/>
+      <c r="O20" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="P20" s="13"/>
-      <c r="Q20" s="3" t="s">
+      <c r="P20" s="21"/>
+      <c r="Q20" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="R20" s="3"/>
+      <c r="R20" s="5"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="13"/>
-      <c r="P21" s="13"/>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="3"/>
+      <c r="A21" s="21"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="21"/>
+      <c r="P21" s="21"/>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="5"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A22" s="3">
+      <c r="A22" s="5">
         <v>5000000</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3">
+      <c r="B22" s="5"/>
+      <c r="C22" s="5">
         <v>1000</v>
       </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3">
+      <c r="D22" s="5"/>
+      <c r="E22" s="5">
         <f>318*8</f>
         <v>2544</v>
       </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3">
+      <c r="F22" s="5"/>
+      <c r="G22" s="5">
         <f>A22/E22</f>
         <v>1965.4088050314465</v>
       </c>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3">
+      <c r="H22" s="5"/>
+      <c r="I22" s="5">
         <f>C22/3600</f>
         <v>0.27777777777777779</v>
       </c>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3">
+      <c r="J22" s="5"/>
+      <c r="K22" s="5">
         <f>I22*(180/0.03)</f>
         <v>1666.6666666666667</v>
       </c>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3">
+      <c r="L22" s="5"/>
+      <c r="M22" s="5">
         <f>K22/G22</f>
         <v>0.84800000000000009</v>
       </c>
-      <c r="N22" s="3"/>
-      <c r="O22" s="3">
+      <c r="N22" s="5"/>
+      <c r="O22" s="5">
         <v>0</v>
       </c>
-      <c r="P22" s="3"/>
-      <c r="Q22" s="3">
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5">
         <f>1-EXP(1)^(-$G$22*(1-$M$22)*O22)</f>
         <v>0</v>
       </c>
-      <c r="R22" s="3"/>
+      <c r="R22" s="5"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
@@ -5848,15 +5931,15 @@
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
-      <c r="O23" s="3">
+      <c r="O23" s="5">
         <v>1E-3</v>
       </c>
-      <c r="P23" s="3"/>
-      <c r="Q23" s="3">
+      <c r="P23" s="5"/>
+      <c r="Q23" s="5">
         <f t="shared" ref="Q23:Q33" si="1">1-EXP(1)^(-$G$22*(1-$M$22)*O23)</f>
         <v>0.25824934618682516</v>
       </c>
-      <c r="R23" s="3"/>
+      <c r="R23" s="5"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
@@ -5869,15 +5952,15 @@
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
-      <c r="O24" s="11">
+      <c r="O24" s="13">
         <v>2E-3</v>
       </c>
-      <c r="P24" s="12"/>
-      <c r="Q24" s="3">
+      <c r="P24" s="14"/>
+      <c r="Q24" s="5">
         <f t="shared" si="1"/>
         <v>0.44980596756772784</v>
       </c>
-      <c r="R24" s="3"/>
+      <c r="R24" s="5"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
@@ -5890,15 +5973,15 @@
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
-      <c r="O25" s="11">
+      <c r="O25" s="13">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="P25" s="12"/>
-      <c r="Q25" s="3">
+      <c r="P25" s="14"/>
+      <c r="Q25" s="5">
         <f t="shared" si="1"/>
         <v>0.59189321671925499</v>
       </c>
-      <c r="R25" s="3"/>
+      <c r="R25" s="5"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
@@ -5911,15 +5994,15 @@
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
-      <c r="O26" s="11">
+      <c r="O26" s="13">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="P26" s="12"/>
-      <c r="Q26" s="3">
+      <c r="P26" s="14"/>
+      <c r="Q26" s="5">
         <f t="shared" si="1"/>
         <v>0.69728652667591584</v>
       </c>
-      <c r="R26" s="3"/>
+      <c r="R26" s="5"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
@@ -5932,15 +6015,15 @@
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
-      <c r="O27" s="11">
+      <c r="O27" s="13">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="P27" s="12"/>
-      <c r="Q27" s="3">
+      <c r="P27" s="14"/>
+      <c r="Q27" s="5">
         <f t="shared" si="1"/>
         <v>0.7754620832438035</v>
       </c>
-      <c r="R27" s="3"/>
+      <c r="R27" s="5"/>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
@@ -5953,15 +6036,15 @@
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
-      <c r="O28" s="11">
+      <c r="O28" s="13">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="P28" s="12"/>
-      <c r="Q28" s="3">
+      <c r="P28" s="14"/>
+      <c r="Q28" s="5">
         <f t="shared" si="1"/>
         <v>0.833448853440243</v>
       </c>
-      <c r="R28" s="3"/>
+      <c r="R28" s="5"/>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
@@ -5974,15 +6057,15 @@
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
-      <c r="O29" s="11">
+      <c r="O29" s="13">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="P29" s="12"/>
-      <c r="Q29" s="3">
+      <c r="P29" s="14"/>
+      <c r="Q29" s="5">
         <f t="shared" si="1"/>
         <v>0.87646057814596645</v>
       </c>
-      <c r="R29" s="3"/>
+      <c r="R29" s="5"/>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
@@ -5995,15 +6078,15 @@
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
-      <c r="O30" s="11">
+      <c r="O30" s="13">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="P30" s="12"/>
-      <c r="Q30" s="3">
+      <c r="P30" s="14"/>
+      <c r="Q30" s="5">
         <f t="shared" si="1"/>
         <v>0.90836455306806896</v>
       </c>
-      <c r="R30" s="3"/>
+      <c r="R30" s="5"/>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
@@ -6016,15 +6099,15 @@
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
-      <c r="O31" s="11">
+      <c r="O31" s="13">
         <v>0.01</v>
       </c>
-      <c r="P31" s="12"/>
-      <c r="Q31" s="3">
+      <c r="P31" s="14"/>
+      <c r="Q31" s="5">
         <f t="shared" si="1"/>
         <v>0.9495827239387874</v>
       </c>
-      <c r="R31" s="3"/>
+      <c r="R31" s="5"/>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
@@ -6037,15 +6120,15 @@
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
-      <c r="O32" s="11">
+      <c r="O32" s="13">
         <v>0.02</v>
       </c>
-      <c r="P32" s="12"/>
-      <c r="Q32" s="3">
+      <c r="P32" s="14"/>
+      <c r="Q32" s="5">
         <f t="shared" si="1"/>
         <v>0.99745809827456744</v>
       </c>
-      <c r="R32" s="3"/>
+      <c r="R32" s="5"/>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
@@ -6058,72 +6141,24 @@
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
-      <c r="O33" s="11">
+      <c r="O33" s="13">
         <v>0.03</v>
       </c>
-      <c r="P33" s="12"/>
-      <c r="Q33" s="3">
+      <c r="P33" s="14"/>
+      <c r="Q33" s="5">
         <f t="shared" si="1"/>
         <v>0.99987184423898845</v>
       </c>
-      <c r="R33" s="3"/>
+      <c r="R33" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="80">
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="Q31:R31"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="Q32:R32"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="Q33:R33"/>
-    <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="Q30:R30"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="O27:P27"/>
-    <mergeCell ref="O28:P28"/>
-    <mergeCell ref="O29:P29"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="Q22:R22"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="O22:P22"/>
-    <mergeCell ref="O23:P23"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="Q11:R11"/>
-    <mergeCell ref="Q12:R12"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="Q14:R14"/>
-    <mergeCell ref="A20:B21"/>
-    <mergeCell ref="C20:D21"/>
-    <mergeCell ref="E20:F21"/>
-    <mergeCell ref="G20:H21"/>
-    <mergeCell ref="I20:J21"/>
-    <mergeCell ref="K20:L21"/>
-    <mergeCell ref="M20:N21"/>
-    <mergeCell ref="O20:P21"/>
-    <mergeCell ref="Q20:R21"/>
-    <mergeCell ref="Q6:R6"/>
-    <mergeCell ref="Q7:R7"/>
-    <mergeCell ref="Q8:R8"/>
-    <mergeCell ref="Q9:R9"/>
-    <mergeCell ref="Q10:R10"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="Q1:R2"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="Q5:R5"/>
+    <mergeCell ref="O14:P14"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="O9:P9"/>
+    <mergeCell ref="O10:P10"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="G1:H2"/>
@@ -6140,16 +6175,64 @@
     <mergeCell ref="M1:N2"/>
     <mergeCell ref="M3:N3"/>
     <mergeCell ref="O1:P2"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="Q1:R2"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="Q5:R5"/>
     <mergeCell ref="O5:P5"/>
-    <mergeCell ref="O6:P6"/>
-    <mergeCell ref="O7:P7"/>
-    <mergeCell ref="O8:P8"/>
-    <mergeCell ref="O9:P9"/>
-    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="Q8:R8"/>
+    <mergeCell ref="Q9:R9"/>
+    <mergeCell ref="Q10:R10"/>
+    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="Q12:R12"/>
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="Q14:R14"/>
+    <mergeCell ref="A20:B21"/>
+    <mergeCell ref="C20:D21"/>
+    <mergeCell ref="E20:F21"/>
+    <mergeCell ref="G20:H21"/>
+    <mergeCell ref="I20:J21"/>
+    <mergeCell ref="K20:L21"/>
+    <mergeCell ref="M20:N21"/>
+    <mergeCell ref="O20:P21"/>
+    <mergeCell ref="Q20:R21"/>
     <mergeCell ref="O11:P11"/>
     <mergeCell ref="O12:P12"/>
     <mergeCell ref="O13:P13"/>
-    <mergeCell ref="O14:P14"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="Q22:R22"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="O22:P22"/>
+    <mergeCell ref="O23:P23"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="Q30:R30"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="Q32:R32"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="Q33:R33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
